--- a/shop-prices.xlsx
+++ b/shop-prices.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
